--- a/data/trans_orig/P79A9_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P79A9_2023-Edad-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>995</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>995</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>995</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>995</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>995</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>995</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>995</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>995</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>65,37%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>78,57%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>815</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,11%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
